--- a/output/EmailAuditSummary.xlsx
+++ b/output/EmailAuditSummary.xlsx
@@ -9,13 +9,13 @@
     <sheet name="Audit Results" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Audit Results'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'Audit Results'!$A$1:$F$28</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="34">
   <si>
     <t>File</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Technical Details</t>
   </si>
   <si>
-    <t>enterprise-newsletter.html</t>
+    <t>Perfect Email.html</t>
   </si>
   <si>
     <t>ACCESSIBILITY_AXE</t>
@@ -44,94 +44,76 @@
     <t>CRITICAL</t>
   </si>
   <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ALT_TEXT_VALIDATION</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>BROKEN_ANCHOR</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>CTA_VALIDATION</t>
+  </si>
+  <si>
+    <t>CONTENT_VALIDATION</t>
+  </si>
+  <si>
+    <t>DUPLICATE_ID</t>
+  </si>
+  <si>
+    <t>LINK_TEXT_VALIDATION</t>
+  </si>
+  <si>
+    <t>LINK_VALIDATION</t>
+  </si>
+  <si>
+    <t>HEADING_HIERARCHY</t>
+  </si>
+  <si>
+    <t>marketing-campaign.html</t>
+  </si>
+  <si>
     <t>FAIL</t>
   </si>
   <si>
+    <t>Image accessibility issue detected</t>
+  </si>
+  <si>
+    <t>[SERIOUS] html-has-lang – Ensure every HTML document has a lang attribute | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/html-has-lang?application=PlaywrightJava; [CRITICAL] image-alt – Ensure &lt;img&gt; elements have alternate text or a role of none or presentation | nodes: img | help: https://dequeuniversity.com/rules/axe/4.10/image-alt?application=PlaywrightJava; [MODERATE] landmark-one-main – Ensure the document has a main landmark | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/landmark-one-main?application=PlaywrightJava; [MODERATE] region – Ensure all page content is contained by landmarks | nodes: h1; img; p:nth-child(3); p:nth-child(4); p:nth-child(5) … (+3 more) | help: https://dequeuniversity.com/rules/axe/4.10/region?application=PlaywrightJava</t>
+  </si>
+  <si>
+    <t>Missing alt attribute on image: https://picsum.photos/600/300</t>
+  </si>
+  <si>
+    <t>Links use unclear or non-descriptive text</t>
+  </si>
+  <si>
+    <t>Generic link text "Read More" for href="" – use descriptive text that conveys the link's destination out of context.</t>
+  </si>
+  <si>
+    <t>One or more hyperlinks are broken</t>
+  </si>
+  <si>
+    <t>3 broken link(s) detected: https://this-link-does-not-exist-123456.com/ → UnknownHostException: this-link-does-not-exist-123456.com | https://invalid-domain-acxiom-demo.com/ → UnknownHostException: invalid-domain-acxiom-demo.com | https://www.example.com/unsubscribe → HTTP 404 (broken)</t>
+  </si>
+  <si>
+    <t>welcome-email.html</t>
+  </si>
+  <si>
     <t>Accessibility compliance issues detected</t>
   </si>
   <si>
     <t>[SERIOUS] html-has-lang – Ensure every HTML document has a lang attribute | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/html-has-lang?application=PlaywrightJava; [MODERATE] landmark-one-main – Ensure the document has a main landmark | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/landmark-one-main?application=PlaywrightJava; [MODERATE] region – Ensure all page content is contained by landmarks | nodes: table | help: https://dequeuniversity.com/rules/axe/4.10/region?application=PlaywrightJava</t>
-  </si>
-  <si>
-    <t>ALT_TEXT_VALIDATION</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>BROKEN_ANCHOR</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>CTA_VALIDATION</t>
-  </si>
-  <si>
-    <t>CONTENT_VALIDATION</t>
-  </si>
-  <si>
-    <t>DUPLICATE_ID</t>
-  </si>
-  <si>
-    <t>LINK_TEXT_VALIDATION</t>
-  </si>
-  <si>
-    <t>LINK_VALIDATION</t>
-  </si>
-  <si>
-    <t>One or more hyperlinks are broken</t>
-  </si>
-  <si>
-    <t>3 broken link(s) detected: https://broken-link-demo-123456.com/ → UnknownHostException: broken-link-demo-123456.com | https://twitter.com/ → HTTP 403 (broken) | https://www.acxiom.com/unsubscribe → HTTP 404 (broken)</t>
-  </si>
-  <si>
-    <t>HEADING_HIERARCHY</t>
-  </si>
-  <si>
-    <t>accessibility-test.html</t>
-  </si>
-  <si>
-    <t>Image accessibility issue detected</t>
-  </si>
-  <si>
-    <t>[SERIOUS] color-contrast – Ensure the contrast between foreground and background colors meets WCAG 2 AA minimum contrast ratio thresholds | nodes: h1; p:nth-child(4); h4; p:nth-child(6) | help: https://dequeuniversity.com/rules/axe/4.10/color-contrast?application=PlaywrightJava; [MODERATE] heading-order – Ensure the order of headings is semantically correct | nodes: h4 | help: https://dequeuniversity.com/rules/axe/4.10/heading-order?application=PlaywrightJava; [SERIOUS] html-has-lang – Ensure every HTML document has a lang attribute | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/html-has-lang?application=PlaywrightJava; [CRITICAL] image-alt – Ensure &lt;img&gt; elements have alternate text or a role of none or presentation | nodes: img[src="https://picsum.photos/400/150"] | help: https://dequeuniversity.com/rules/axe/4.10/image-alt?application=PlaywrightJava; [MODERATE] landmark-one-main – Ensure the document has a main landmark | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/landmark-one-main?application=PlaywrightJava; [MODERATE] region – Ensure all page content is contained by landmarks | nodes: h1; img[src="https://picsum.photos/400/150"]; p:nth-child(4); h4; p:nth-child(6) … (+2 more) | help: https://dequeuniversity.com/rules/axe/4.10/region?application=PlaywrightJava</t>
-  </si>
-  <si>
-    <t>Empty alt attribute on image: https://picsum.photos/500/200; Missing alt attribute on image: https://picsum.photos/400/150</t>
-  </si>
-  <si>
-    <t>Links use unclear or non-descriptive text</t>
-  </si>
-  <si>
-    <t>Generic link text "Learn More" for href="https://www.acxiom.com" – use descriptive text that conveys the link's destination out of context.</t>
-  </si>
-  <si>
-    <t>1 broken link(s) detected: https://www.acxiom.com/unsubscribe → HTTP 404 (broken)</t>
-  </si>
-  <si>
-    <t>Skipped heading level: &lt;h4&gt; "Incorrect Heading Hierarchy" follows &lt;h1&gt; "Accessibility Test Email" (expected &lt;h2&gt;)</t>
-  </si>
-  <si>
-    <t>duplicate-id-test.html</t>
-  </si>
-  <si>
-    <t>[SERIOUS] html-has-lang – Ensure every HTML document has a lang attribute | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/html-has-lang?application=PlaywrightJava; [MODERATE] landmark-one-main – Ensure the document has a main landmark | nodes: html | help: https://dequeuniversity.com/rules/axe/4.10/landmark-one-main?application=PlaywrightJava; [MODERATE] region – Ensure all page content is contained by landmarks | nodes: #mainTitle; div:nth-child(2); div:nth-child(3); p:nth-child(6); p:nth-child(7) … (+1 more) | help: https://dequeuniversity.com/rules/axe/4.10/region?application=PlaywrightJava</t>
-  </si>
-  <si>
-    <t>Call-to-action issue detected</t>
-  </si>
-  <si>
-    <t>Duplicate id 'promoBlock' found 2 times; Duplicate id 'ctaButton' found 2 times</t>
-  </si>
-  <si>
-    <t>welcome-email.html</t>
   </si>
   <si>
     <t>2 broken link(s) detected: https://www.acxiom.com/preferences → HTTP 404 (broken) | https://www.acxiom.com/unsubscribe → HTTP 404 (broken)</t>
@@ -258,10 +240,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="21.52734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="21.09375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="19.37890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="7.93359375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="5.59765625" customWidth="true" bestFit="true"/>
@@ -299,14 +281,14 @@
       <c r="C2" t="s" s="1">
         <v>8</v>
       </c>
-      <c r="D2" t="s" s="7">
+      <c r="D2" t="s" s="6">
         <v>9</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -314,19 +296,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -334,19 +316,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -354,19 +336,19 @@
         <v>6</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -374,19 +356,19 @@
         <v>6</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -394,19 +376,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -414,19 +396,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -434,19 +416,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s" s="7">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s" s="6">
         <v>9</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -454,24 +436,24 @@
         <v>6</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>7</v>
@@ -480,178 +462,178 @@
         <v>8</v>
       </c>
       <c r="D11" t="s" s="7">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s" s="7">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s" s="3">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s" s="7">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B17" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s" s="7">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="F17" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s" s="7">
         <v>22</v>
       </c>
-      <c r="C18" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s" s="7">
-        <v>9</v>
-      </c>
       <c r="E18" t="s" s="0">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s" s="7">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s" s="6">
         <v>9</v>
       </c>
       <c r="E19" t="s" s="0">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s" s="0">
         <v>7</v>
@@ -660,357 +642,177 @@
         <v>8</v>
       </c>
       <c r="D20" t="s" s="7">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s" s="7">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s" s="6">
         <v>9</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s" s="7">
         <v>22</v>
       </c>
-      <c r="C27" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s" s="7">
-        <v>9</v>
-      </c>
       <c r="E27" t="s" s="0">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s" s="6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B29" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C29" t="s" s="1">
-        <v>8</v>
-      </c>
-      <c r="D29" t="s" s="7">
-        <v>9</v>
-      </c>
-      <c r="E29" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B30" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s" s="6">
-        <v>14</v>
-      </c>
-      <c r="E30" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D31" t="s" s="6">
-        <v>14</v>
-      </c>
-      <c r="E31" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F31" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D32" t="s" s="6">
-        <v>14</v>
-      </c>
-      <c r="E32" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s" s="6">
-        <v>14</v>
-      </c>
-      <c r="E33" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F33" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B34" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="C34" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D34" t="s" s="6">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F34" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B35" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="C35" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D35" t="s" s="6">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B36" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s" s="7">
-        <v>9</v>
-      </c>
-      <c r="E36" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="F36" t="s" s="0">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B37" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C37" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D37" t="s" s="6">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>